--- a/server/src/main/resources/template/武将胜率统计模版.xlsx
+++ b/server/src/main/resources/template/武将胜率统计模版.xlsx
@@ -30,9 +30,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
-  <si>
-    <t>若武将总场数&gt;10场，胜率最高身份/位置 &gt; 60，则武将将池升一级，胜率最低身份/位置 &lt; 40，则武将将池降一级</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
+  <si>
+    <t>若最高胜率总场数&gt;10场，胜率最高身份/位置 &gt; 60，则武将将池升一级，胜率最低身份/位置 &lt; 40，则武将将池降一级</t>
   </si>
   <si>
     <t>武将</t>
@@ -41,7 +41,7 @@
     <t>将池</t>
   </si>
   <si>
-    <t>总场数</t>
+    <t>最高胜率总场数</t>
   </si>
   <si>
     <t>胜率最高身份/位置</t>
@@ -144,6 +144,117 @@
   </si>
   <si>
     <t>四号位胜率</t>
+  </si>
+  <si>
+    <t>{.hero}</t>
+  </si>
+  <si>
+    <t>{.pool}</t>
+  </si>
+  <si>
+    <t>{.bestRoleTotal}</t>
+  </si>
+  <si>
+    <t>{.bestRole}</t>
+  </si>
+  <si>
+    <t>{.bestRate}</t>
+  </si>
+  <si>
+    <t>{.worstRole}</t>
+  </si>
+  <si>
+    <t>{.worstRate}</t>
+  </si>
+  <si>
+    <t>{.landlordWin}</t>
+  </si>
+  <si>
+    <t>{.landlordLose}</t>
+  </si>
+  <si>
+    <t>{.landlordRate}</t>
+  </si>
+  <si>
+    <t>{.farmerWin}</t>
+  </si>
+  <si>
+    <t>{.farmerLose}</t>
+  </si>
+  <si>
+    <t>{.farmerRate}</t>
+  </si>
+  <si>
+    <t>{.lordWin}</t>
+  </si>
+  <si>
+    <t>{.lordLose}</t>
+  </si>
+  <si>
+    <t>{.lordRate}</t>
+  </si>
+  <si>
+    <t>{.loyalistWin}</t>
+  </si>
+  <si>
+    <t>{.loyalistLose}</t>
+  </si>
+  <si>
+    <t>{.loyalistRate}</t>
+  </si>
+  <si>
+    <t>{.rebelWin}</t>
+  </si>
+  <si>
+    <t>{.rebelLose}</t>
+  </si>
+  <si>
+    <t>{.rebelRate}</t>
+  </si>
+  <si>
+    <t>{.traitorWin}</t>
+  </si>
+  <si>
+    <t>{.traitorLose}</t>
+  </si>
+  <si>
+    <t>{.traitorRate}</t>
+  </si>
+  <si>
+    <t>{.seat1Win}</t>
+  </si>
+  <si>
+    <t>{.seat1Lose}</t>
+  </si>
+  <si>
+    <t>{.seat1Rate}</t>
+  </si>
+  <si>
+    <t>{.seat2Win}</t>
+  </si>
+  <si>
+    <t>{.seat2Lose}</t>
+  </si>
+  <si>
+    <t>{.seat2Rate}</t>
+  </si>
+  <si>
+    <t>{.seat3Win}</t>
+  </si>
+  <si>
+    <t>{.seat3Lose}</t>
+  </si>
+  <si>
+    <t>{.seat3Rate}</t>
+  </si>
+  <si>
+    <t>{.seat4Win}</t>
+  </si>
+  <si>
+    <t>{.seat4Lose}</t>
+  </si>
+  <si>
+    <t>{.seat4Rate}</t>
   </si>
 </sst>
 </file>
@@ -1380,12 +1491,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AK2"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="1"/>
+  <dimension ref="A1:AK3"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="17.3076923076923" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.97115384615385" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.2980769230769" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19" style="1" customWidth="1"/>
     <col min="4" max="7" width="22.5384615384615" style="1" customWidth="1"/>
     <col min="8" max="25" width="11.1538461538462" style="1" customWidth="1"/>
     <col min="26" max="37" width="13.7692307692308" style="1" customWidth="1"/>
@@ -1546,6 +1657,119 @@
         <v>37</v>
       </c>
     </row>
+    <row r="3" customHeight="1" spans="1:37">
+      <c r="A3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG3" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AI3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK3" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:AK3" etc:filterBottomFollowUsedRange="0">
     <extLst/>

--- a/server/src/main/resources/template/武将胜率统计模版.xlsx
+++ b/server/src/main/resources/template/武将胜率统计模版.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t>若最高胜率总场数&gt;10场，胜率最高身份/位置 &gt; 60，则武将将池升一级，胜率最低身份/位置 &lt; 40，则武将将池降一级</t>
   </si>
@@ -255,6 +255,12 @@
   </si>
   <si>
     <t>{.seat4Rate}</t>
+  </si>
+  <si>
+    <t>最后更新时间</t>
+  </si>
+  <si>
+    <t>{.updatedAt}</t>
   </si>
 </sst>
 </file>
@@ -1491,7 +1497,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AK3"/>
+  <dimension ref="A1:AL3"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="17.3076923076923" style="1" customWidth="1"/>
@@ -1500,10 +1506,11 @@
     <col min="4" max="7" width="22.5384615384615" style="1" customWidth="1"/>
     <col min="8" max="25" width="11.1538461538462" style="1" customWidth="1"/>
     <col min="26" max="37" width="13.7692307692308" style="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.23076923076923" style="1"/>
+    <col min="38" max="38" width="13.7692307692308" style="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.23076923076923" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1" spans="1:37">
+    <row r="1" ht="40" customHeight="1" spans="1:38">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1542,9 +1549,10 @@
       <c r="AH1" s="3"/>
       <c r="AI1" s="3"/>
       <c r="AJ1" s="3"/>
-      <c r="AK1" s="5"/>
+      <c r="AK1" s="3"/>
+      <c r="AL1" s="5"/>
     </row>
-    <row r="2" ht="17.6" spans="1:37">
+    <row r="2" ht="17.6" spans="1:38">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -1656,8 +1664,11 @@
       <c r="AK2" s="4" t="s">
         <v>37</v>
       </c>
+      <c r="AL2" s="4" t="s">
+        <v>75</v>
+      </c>
     </row>
-    <row r="3" customHeight="1" spans="1:37">
+    <row r="3" customHeight="1" spans="1:38">
       <c r="A3" s="1" t="s">
         <v>38</v>
       </c>
@@ -1769,13 +1780,16 @@
       <c r="AK3" s="1" t="s">
         <v>74</v>
       </c>
+      <c r="AL3" s="1" t="s">
+        <v>76</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:AK3" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:AL3" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="1">
-    <mergeCell ref="A1:AK1"/>
+    <mergeCell ref="A1:AL1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/server/src/main/resources/template/武将胜率统计模版.xlsx
+++ b/server/src/main/resources/template/武将胜率统计模版.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25820" windowHeight="13240"/>
+    <workbookView windowWidth="30240" windowHeight="13340"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$AK$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$AL$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -146,6 +146,9 @@
     <t>四号位胜率</t>
   </si>
   <si>
+    <t>最后更新时间</t>
+  </si>
+  <si>
     <t>{.hero}</t>
   </si>
   <si>
@@ -255,9 +258,6 @@
   </si>
   <si>
     <t>{.seat4Rate}</t>
-  </si>
-  <si>
-    <t>最后更新时间</t>
   </si>
   <si>
     <t>{.updatedAt}</t>
@@ -645,7 +645,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -657,43 +657,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -829,7 +792,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -841,34 +804,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -953,24 +916,21 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1506,12 +1466,12 @@
     <col min="4" max="7" width="22.5384615384615" style="1" customWidth="1"/>
     <col min="8" max="25" width="11.1538461538462" style="1" customWidth="1"/>
     <col min="26" max="37" width="13.7692307692308" style="1" customWidth="1"/>
-    <col min="38" max="38" width="13.7692307692308" style="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.23076923076923" style="1"/>
+    <col min="38" max="38" width="16.5384615384615" style="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.23076923076923" style="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1" spans="1:38">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3"/>
@@ -1550,7 +1510,7 @@
       <c r="AI1" s="3"/>
       <c r="AJ1" s="3"/>
       <c r="AK1" s="3"/>
-      <c r="AL1" s="5"/>
+      <c r="AL1" s="3"/>
     </row>
     <row r="2" ht="17.6" spans="1:38">
       <c r="A2" s="4" t="s">
@@ -1665,120 +1625,120 @@
         <v>37</v>
       </c>
       <c r="AL2" s="4" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:38">
       <c r="A3" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AG3" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AH3" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AJ3" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK3" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL3" s="1" t="s">
         <v>76</v>

--- a/server/src/main/resources/template/武将胜率统计模版.xlsx
+++ b/server/src/main/resources/template/武将胜率统计模版.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="13340"/>
+    <workbookView windowWidth="30240" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$AL$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$AM$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
     <t>若最高胜率总场数&gt;10场，胜率最高身份/位置 &gt; 60，则武将将池升一级，胜率最低身份/位置 &lt; 40，则武将将池降一级</t>
   </si>
@@ -146,6 +146,9 @@
     <t>四号位胜率</t>
   </si>
   <si>
+    <t>是否在将池中</t>
+  </si>
+  <si>
     <t>最后更新时间</t>
   </si>
   <si>
@@ -258,6 +261,9 @@
   </si>
   <si>
     <t>{.seat4Rate}</t>
+  </si>
+  <si>
+    <t>{.inPool}</t>
   </si>
   <si>
     <t>{.updatedAt}</t>
@@ -1457,7 +1463,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AL3"/>
+  <dimension ref="A1:AM3"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="17.3076923076923" style="1" customWidth="1"/>
@@ -1465,12 +1471,12 @@
     <col min="3" max="3" width="19" style="1" customWidth="1"/>
     <col min="4" max="7" width="22.5384615384615" style="1" customWidth="1"/>
     <col min="8" max="25" width="11.1538461538462" style="1" customWidth="1"/>
-    <col min="26" max="37" width="13.7692307692308" style="1" customWidth="1"/>
-    <col min="38" max="38" width="16.5384615384615" style="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.23076923076923" style="2"/>
+    <col min="26" max="38" width="13.7692307692308" style="1" customWidth="1"/>
+    <col min="39" max="39" width="16.5384615384615" style="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.23076923076923" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1" spans="1:38">
+    <row r="1" ht="40" customHeight="1" spans="1:39">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1511,8 +1517,9 @@
       <c r="AJ1" s="3"/>
       <c r="AK1" s="3"/>
       <c r="AL1" s="3"/>
+      <c r="AM1" s="3"/>
     </row>
-    <row r="2" ht="17.6" spans="1:38">
+    <row r="2" ht="17.6" spans="1:39">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -1627,129 +1634,135 @@
       <c r="AL2" s="4" t="s">
         <v>38</v>
       </c>
+      <c r="AM2" s="4" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="3" customHeight="1" spans="1:38">
+    <row r="3" customHeight="1" spans="1:39">
       <c r="A3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AG3" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AH3" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AJ3" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AK3" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AL3" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="AM3" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:AL3" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:AM3" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="1">
-    <mergeCell ref="A1:AL1"/>
+    <mergeCell ref="A1:AM1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/server/src/main/resources/template/武将胜率统计模版.xlsx
+++ b/server/src/main/resources/template/武将胜率统计模版.xlsx
@@ -32,7 +32,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
-    <t>若最高胜率总场数&gt;10场，胜率最高身份/位置 &gt; 60，则武将将池升一级，胜率最低身份/位置 &lt; 40，则武将将池降一级</t>
+    <t>武将将池划分遵循以下原则：
+1. 好玩的武将划分到等级尽可能高的将池
+2. 若武将最高胜率总场数&gt;10场，胜率最高身份/位置 &gt; 60，则武将将池升一级，胜率最低身份/位置 &lt; 40，则武将将池降一级</t>
   </si>
   <si>
     <t>武将</t>
@@ -933,7 +935,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1476,7 +1478,7 @@
     <col min="40" max="16384" width="9.23076923076923" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1" spans="1:39">
+    <row r="1" ht="58" customHeight="1" spans="1:39">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
